--- a/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-10T09:51:04+00:00</t>
+    <t>2025-07-18T10:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-18T10:11:50+00:00</t>
+    <t>2025-07-21T08:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T08:51:50+00:00</t>
+    <t>2025-07-23T09:54:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-23T09:54:05+00:00</t>
+    <t>2025-07-23T12:37:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-23T12:37:58+00:00</t>
+    <t>2025-07-29T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
